--- a/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
+++ b/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
@@ -585,16 +585,16 @@
     <t>02_HRvLR_groups/01_Design_Contrasts/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>96ffcae5a944141f3f5c56cd78441410</t>
+    <t>00359ae411e094eedfc9b750b4136ca8</t>
   </si>
   <si>
     <t>module_tests</t>
   </si>
   <si>
-    <t>b773da843c2dcba997325efc4396fd70</t>
-  </si>
-  <si>
-    <t>068c220be1f09313a9955fa01f855602</t>
+    <t>f2cbfa3e9ae7db9f5a02d9b5b30d4c60</t>
+  </si>
+  <si>
+    <t>b928dfb75f0631b92e8ffaf819778f86</t>
   </si>
   <si>
     <t>set_summary</t>
@@ -603,7 +603,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_contrasts.xlsx</t>
   </si>
   <si>
-    <t>8ac2a4ea9daa2c8f0ce9972093b70e94</t>
+    <t>4639754d416bdb38ebf71b68193ad163</t>
   </si>
   <si>
     <t>modules</t>
@@ -615,7 +615,7 @@
     <t>module_labels</t>
   </si>
   <si>
-    <t>01291ab1ce29b17a340d0d6fd1e6df9b</t>
+    <t>4b9f7cd5493b79c191734d7421f3b125</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
+++ b/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
@@ -45,7 +45,7 @@
     <t>panel_a</t>
   </si>
   <si>
-    <t>a: module size, top set and its FDR, three hub proteins, STRING enrichment ratio.</t>
+    <t>a: module size, top set and its FDR, three top members, STRING enrichment ratio.</t>
   </si>
   <si>
     <t>panel_b</t>
@@ -135,7 +135,7 @@
     <t>FDR of the top set.</t>
   </si>
   <si>
-    <t>hubs</t>
+    <t>top_members</t>
   </si>
   <si>
     <t>Members with the highest kME.</t>
@@ -273,10 +273,10 @@
     <t>a</t>
   </si>
   <si>
-    <t>module size, top set and hubs</t>
-  </si>
-  <si>
-    <t>01_Trunk/07_Module_Characterisation/c_data/module_characterisation.xlsx</t>
+    <t>module size, top set and top members</t>
+  </si>
+  <si>
+    <t>01_Processing/07_Module_Characterisation/c_data/module_characterisation.xlsx</t>
   </si>
   <si>
     <t>labels</t>
@@ -321,7 +321,7 @@
     <t>eigengene per person</t>
   </si>
   <si>
-    <t>01_Trunk/06_Module_Building/c_data/modules.rds</t>
+    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
     <t>eigengenes</t>
@@ -615,7 +615,7 @@
     <t>module_labels</t>
   </si>
   <si>
-    <t>4b9f7cd5493b79c191734d7421f3b125</t>
+    <t>3a59bd479a4ab3c42392acd8f78f3eaf</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
+++ b/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
@@ -219,7 +219,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -585,13 +585,13 @@
     <t>02_HRvLR_groups/01_Design_Contrasts/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>00359ae411e094eedfc9b750b4136ca8</t>
+    <t>73c4ee34c170b774306fa764c4157d4a</t>
   </si>
   <si>
     <t>module_tests</t>
   </si>
   <si>
-    <t>f2cbfa3e9ae7db9f5a02d9b5b30d4c60</t>
+    <t>e6fe9468e646c8c29f57c495e3476353</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -603,7 +603,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_contrasts.xlsx</t>
   </si>
   <si>
-    <t>4639754d416bdb38ebf71b68193ad163</t>
+    <t>a26d20d89291145a09301d8252b54d07</t>
   </si>
   <si>
     <t>modules</t>
@@ -615,7 +615,7 @@
     <t>module_labels</t>
   </si>
   <si>
-    <t>3a59bd479a4ab3c42392acd8f78f3eaf</t>
+    <t>111f4c43baff01ed48d9887e90d0e8e4</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
+++ b/02_HRvLR_groups/Figures/F2_Programmes/c_data/f2_programmes.xlsx
@@ -585,13 +585,13 @@
     <t>02_HRvLR_groups/01_Design_Contrasts/c_data/design_contrasts.xlsx</t>
   </si>
   <si>
-    <t>73c4ee34c170b774306fa764c4157d4a</t>
+    <t>39540089eab402ee5a70d7765367711f</t>
   </si>
   <si>
     <t>module_tests</t>
   </si>
   <si>
-    <t>e6fe9468e646c8c29f57c495e3476353</t>
+    <t>d34ea4613b20d81703717017a28b09a7</t>
   </si>
   <si>
     <t>b928dfb75f0631b92e8ffaf819778f86</t>
@@ -603,7 +603,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_contrasts.xlsx</t>
   </si>
   <si>
-    <t>a26d20d89291145a09301d8252b54d07</t>
+    <t>4881d4307de24d7bff3c51428ffaaf37</t>
   </si>
   <si>
     <t>modules</t>
@@ -615,7 +615,7 @@
     <t>module_labels</t>
   </si>
   <si>
-    <t>111f4c43baff01ed48d9887e90d0e8e4</t>
+    <t>218ea5b0a99df49bcf01bd7e91c02753</t>
   </si>
   <si>
     <t>BiocGenerics</t>
